--- a/templates/chicken_bone analyziz.xlsx
+++ b/templates/chicken_bone analyziz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sderhami/Documents/Apps/nutDataGen/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9FBD31-9F03-A846-A000-BE6F773CA2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFB9D05-418A-EA41-A5FA-49E60048B140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-41020" yWindow="3060" windowWidth="32740" windowHeight="21240" xr2:uid="{CA982CCA-F52D-EB4A-A696-24CC6C7FDE8E}"/>
+    <workbookView xWindow="-48400" yWindow="3060" windowWidth="40120" windowHeight="21240" xr2:uid="{CA982CCA-F52D-EB4A-A696-24CC6C7FDE8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="102">
   <si>
     <t>chicken bones raw</t>
   </si>
@@ -344,6 +344,12 @@
   </si>
   <si>
     <t>ai_source</t>
+  </si>
+  <si>
+    <t>total PUFA</t>
+  </si>
+  <si>
+    <t>DPA (22:5n-3)</t>
   </si>
 </sst>
 </file>
@@ -393,7 +399,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -416,11 +422,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -434,6 +451,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -749,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4327CF7A-B990-F44A-99E3-5340363B09BB}">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -2412,6 +2432,48 @@
         <v>15.93</v>
       </c>
     </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D52">
+        <v>1293</v>
+      </c>
+      <c r="F52" t="s">
+        <v>100</v>
+      </c>
+      <c r="G52" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+      <c r="I52" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="J52">
+        <f>I52*H52</f>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D53">
+        <v>1280</v>
+      </c>
+      <c r="F53" t="s">
+        <v>101</v>
+      </c>
+      <c r="G53" t="s">
+        <v>3</v>
+      </c>
+      <c r="H53">
+        <v>6.2E-2</v>
+      </c>
+      <c r="I53" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="J53">
+        <f>I53*H53</f>
+        <v>4.9600000000000005E-2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
